--- a/ig/DM-JUILLET-2026/CodeSystem-TRE-R212-Equipement.xlsx
+++ b/ig/DM-JUILLET-2026/CodeSystem-TRE-R212-Equipement.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260730120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2026-07-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -652,7 +652,7 @@
     <t>072</t>
   </si>
   <si>
-    <t>Table de bloc opératoire obésité (poids &gt; 250 kg) - bariatrique</t>
+    <t>Table de bloc opératoire obésité (poids supérieur à 250 kg) - bariatrique</t>
   </si>
   <si>
     <t>073</t>
@@ -724,7 +724,7 @@
     <t>084</t>
   </si>
   <si>
-    <t>Table de radiologie obésité (poids &gt; 250 kg) - bariatrique</t>
+    <t>Table de radiologie interventionnelle obésité (poids supérieur à 250 kg) - bariatrique</t>
   </si>
   <si>
     <t>085</t>
@@ -1033,7 +1033,7 @@
     <t>130</t>
   </si>
   <si>
-    <t>Chambre et locaux sécurisés permettant la PEC des personnes à risque suicidaire</t>
+    <t>Chambre et locaux sécurisés permettant la prise en charge des personnes à risque suicidaire</t>
   </si>
   <si>
     <t>131</t>
@@ -1135,7 +1135,7 @@
     <t>147</t>
   </si>
   <si>
-    <t>Espace de calme-retrait, apaisement</t>
+    <t>Espace de calme-retrait, d'apaisement</t>
   </si>
   <si>
     <t>148</t>
@@ -1366,7 +1366,7 @@
     <t>184</t>
   </si>
   <si>
-    <t>Dispositif de réadaptation à la marche par allègement du poids du corps</t>
+    <t>Dispositif de réadaptation à la marche par allègement du poids du corps (anti-gravité)</t>
   </si>
   <si>
     <t>185</t>

--- a/ig/DM-JUILLET-2026/CodeSystem-TRE-R212-Equipement.xlsx
+++ b/ig/DM-JUILLET-2026/CodeSystem-TRE-R212-Equipement.xlsx
@@ -652,7 +652,7 @@
     <t>072</t>
   </si>
   <si>
-    <t>Table de bloc opératoire obésité (poids supérieur à 250 kg) - bariatrique</t>
+    <t>Table de bloc opératoire obésité (poids &gt; 250 kg) - bariatrique</t>
   </si>
   <si>
     <t>073</t>
